--- a/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
@@ -854,9 +854,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,18 +876,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1192,48 +1192,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="53"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="54"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="I3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="53"/>
+      <c r="J3" s="54"/>
       <c r="K3" s="3" t="s">
         <v>58</v>
       </c>
@@ -1274,11 +1274,11 @@
       <c r="P3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="Q3" s="53"/>
+      <c r="Q3" s="54"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="32">
         <v>10</v>
       </c>
@@ -1306,21 +1306,21 @@
         <f>C4</f>
         <v>10</v>
       </c>
-      <c r="J4" s="53"/>
+      <c r="J4" s="54"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="54"/>
       <c r="S4" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
@@ -1346,7 +1346,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="J5" s="53"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1365,7 +1365,7 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="53"/>
+      <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1375,20 +1375,20 @@
         <v>8</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="53"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1457,7 +1457,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="53"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1495,7 +1495,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="53"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1535,7 +1535,7 @@
         <f>B10</f>
         <v>10</v>
       </c>
-      <c r="J10" s="53"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="53"/>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1560,10 +1560,7 @@
       <c r="C11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="29">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="D11" s="29"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6">
         <f>B11</f>
@@ -1572,7 +1569,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1581,7 +1578,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="53"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1593,10 +1590,7 @@
       <c r="C12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="29">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
+      <c r="D12" s="29"/>
       <c r="E12" s="38">
         <f>B12</f>
         <v>13</v>
@@ -1608,7 +1602,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1619,7 +1613,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="53"/>
+      <c r="Q12" s="54"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1631,10 +1625,7 @@
       <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="29">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
+      <c r="D13" s="29"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
@@ -1643,7 +1634,7 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="53"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1652,7 +1643,7 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="53"/>
+      <c r="Q13" s="54"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1664,10 +1655,7 @@
       <c r="C14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="29">
-        <f t="shared" si="1"/>
-        <v>11.5</v>
-      </c>
+      <c r="D14" s="29"/>
       <c r="E14" s="6">
         <f>B14</f>
         <v>11.5</v>
@@ -1679,7 +1667,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1690,7 +1678,7 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="53"/>
+      <c r="Q14" s="54"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1702,10 +1690,7 @@
       <c r="C15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="29">
-        <f t="shared" si="1"/>
-        <v>5.5</v>
-      </c>
+      <c r="D15" s="29"/>
       <c r="E15" s="6">
         <f>B15</f>
         <v>5.5</v>
@@ -1720,7 +1705,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="53"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1733,7 +1718,7 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="53"/>
+      <c r="Q15" s="54"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1745,10 +1730,7 @@
       <c r="C16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="29">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
+      <c r="D16" s="29"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -1763,7 +1745,7 @@
         <f>B16</f>
         <v>10</v>
       </c>
-      <c r="J16" s="53"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1776,7 +1758,7 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="53"/>
+      <c r="Q16" s="54"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1803,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1816,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="53"/>
+      <c r="Q17" s="54"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1828,10 +1810,7 @@
       <c r="C18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="23">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="D18" s="23"/>
       <c r="E18" s="6">
         <f>B18</f>
         <v>5</v>
@@ -1840,10 +1819,7 @@
         <f>B18</f>
         <v>5</v>
       </c>
-      <c r="G18" s="6">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="G18" s="6"/>
       <c r="H18" s="6">
         <f>B18</f>
         <v>5</v>
@@ -1852,7 +1828,7 @@
         <f>B18</f>
         <v>5</v>
       </c>
-      <c r="J18" s="53"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1867,7 +1843,7 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="53"/>
+      <c r="Q18" s="54"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1879,16 +1855,10 @@
       <c r="C19" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="29">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
+      <c r="D19" s="29"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="6">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="G19" s="6"/>
       <c r="H19" s="6">
         <f>B19</f>
         <v>10</v>
@@ -1897,7 +1867,7 @@
         <f>B19</f>
         <v>10</v>
       </c>
-      <c r="J19" s="53"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1908,7 +1878,7 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="53"/>
+      <c r="Q19" s="54"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1920,25 +1890,16 @@
       <c r="C20" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="33">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
+      <c r="D20" s="33"/>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
-      <c r="G20" s="34">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H20" s="34">
-        <f>B20</f>
-        <v>10</v>
-      </c>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="35">
         <f>B20</f>
         <v>10</v>
       </c>
-      <c r="J20" s="53"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1947,12 +1908,12 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="53"/>
+      <c r="Q20" s="54"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="56"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="3">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
         <v>10.833333333333334</v>
@@ -1977,7 +1938,7 @@
         <f t="shared" si="3"/>
         <v>9.3333333333333339</v>
       </c>
-      <c r="J21" s="53"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1996,7 +1957,7 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="53"/>
+      <c r="Q21" s="54"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2031,7 +1992,7 @@
         <f t="shared" si="4"/>
         <v>9.6</v>
       </c>
-      <c r="J22" s="53"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -2050,85 +2011,85 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="53"/>
+      <c r="Q22" s="54"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
@@ -2151,7 +2112,7 @@
       <c r="I27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="53"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="9" t="s">
         <v>0</v>
       </c>
@@ -2170,7 +2131,7 @@
       <c r="P27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="53"/>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
@@ -2204,7 +2165,7 @@
         <f>C28</f>
         <v>10</v>
       </c>
-      <c r="J28" s="53"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2223,7 +2184,7 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="53"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
@@ -2257,7 +2218,7 @@
         <f>C29</f>
         <v>10</v>
       </c>
-      <c r="J29" s="53"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2276,7 +2237,7 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="53"/>
+      <c r="Q29" s="54"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
@@ -2310,7 +2271,7 @@
         <f>C30</f>
         <v>10</v>
       </c>
-      <c r="J30" s="53"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2329,7 +2290,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="53"/>
+      <c r="Q30" s="54"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2359,7 +2320,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="J31" s="53"/>
+      <c r="J31" s="54"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2378,7 +2339,7 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="53"/>
+      <c r="Q31" s="54"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -2388,20 +2349,20 @@
         <v>8</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="54"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2428,7 +2389,7 @@
         <f>$B33</f>
         <v>10</v>
       </c>
-      <c r="J33" s="53"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2441,7 +2402,7 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="53"/>
+      <c r="Q33" s="54"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2465,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="53"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2476,7 +2437,7 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="53"/>
+      <c r="Q34" s="54"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2497,7 +2458,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="53"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2506,7 +2467,7 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="53"/>
+      <c r="Q35" s="54"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2527,7 +2488,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="53"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2536,7 +2497,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="53"/>
+      <c r="Q36" s="54"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2560,7 +2521,7 @@
         <f>$B37</f>
         <v>10</v>
       </c>
-      <c r="J37" s="53"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2571,7 +2532,7 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="53"/>
+      <c r="Q37" s="54"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2595,7 +2556,7 @@
         <f>B38</f>
         <v>10</v>
       </c>
-      <c r="J38" s="53"/>
+      <c r="J38" s="54"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2606,7 +2567,7 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="53"/>
+      <c r="Q38" s="54"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2627,7 +2588,7 @@
         <f>$B39</f>
         <v>10</v>
       </c>
-      <c r="J39" s="53"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2636,7 +2597,7 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="53"/>
+      <c r="Q39" s="54"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2657,7 +2618,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="53"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2666,7 +2627,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="53"/>
+      <c r="Q40" s="54"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2690,7 +2651,7 @@
         <v>10</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="53"/>
+      <c r="J41" s="54"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2701,7 +2662,7 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="53"/>
+      <c r="Q41" s="54"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -2731,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="53"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2746,7 +2707,7 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="53"/>
+      <c r="Q42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2776,7 +2737,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="53"/>
+      <c r="J43" s="54"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2791,7 +2752,7 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="53"/>
+      <c r="Q43" s="54"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2812,7 +2773,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2821,12 +2782,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="53"/>
+      <c r="Q44" s="54"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="6">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>10</v>
@@ -2851,7 +2812,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="J45" s="53"/>
+      <c r="J45" s="54"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2870,7 +2831,7 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="53"/>
+      <c r="Q45" s="54"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -2905,7 +2866,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="J46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2924,128 +2885,128 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="53"/>
+      <c r="Q46" s="54"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="53"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="53"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="53"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="59" t="s">
+      <c r="A51" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="59"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="53"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="53"/>
+      <c r="P51" s="53"/>
+      <c r="Q51" s="54"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="55"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="53"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="54"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="3" t="s">
         <v>0</v>
       </c>
@@ -3064,19 +3025,19 @@
       <c r="I53" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
-      <c r="N53" s="53"/>
-      <c r="O53" s="53"/>
-      <c r="P53" s="53"/>
-      <c r="Q53" s="53"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="54"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="54"/>
+      <c r="Q53" s="54"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="8">(D46+D22)/2</f>
         <v>10.25</v>
@@ -3101,60 +3062,55 @@
         <f t="shared" si="8"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="J54" s="53"/>
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-      <c r="N54" s="53"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="53"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="54"/>
+      <c r="Q54" s="54"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="54"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="53"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3171,6 +3127,11 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">

--- a/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
@@ -854,28 +854,28 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1192,48 +1192,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="54"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="53"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="I3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="54"/>
+      <c r="J3" s="53"/>
       <c r="K3" s="3" t="s">
         <v>58</v>
       </c>
@@ -1274,79 +1274,79 @@
       <c r="P3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="Q3" s="54"/>
+      <c r="Q3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="32">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="39">
         <f>C4</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E4" s="40">
         <f>C4</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F4" s="40">
         <f>C4</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" s="40">
         <f>C4</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H4" s="40">
         <f>C4</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I4" s="41">
         <f>C4</f>
-        <v>10</v>
-      </c>
-      <c r="J4" s="54"/>
+        <v>14</v>
+      </c>
+      <c r="J4" s="53"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="53"/>
       <c r="S4" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" ref="E5:I5" si="0">(E4*L5)/L5</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" s="21">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" s="21">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H5" s="21">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I5" s="22">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="J5" s="54"/>
+        <v>14</v>
+      </c>
+      <c r="J5" s="53"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1365,7 +1365,7 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="54"/>
+      <c r="Q5" s="53"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1375,50 +1375,50 @@
         <v>8</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="54"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="53"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="32">
-        <v>12</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="25">
-        <f t="shared" ref="D7:D20" si="1">B7</f>
-        <v>12</v>
+        <f t="shared" ref="D7:D17" si="1">B7</f>
+        <v>16.899999999999999</v>
       </c>
       <c r="E7" s="27">
         <f>B7</f>
-        <v>12</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F7" s="27">
         <f>B7</f>
-        <v>12</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="G7" s="27">
         <f>B7</f>
-        <v>12</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="54"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="54"/>
+      <c r="Q7" s="53"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1457,7 +1457,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="54"/>
+      <c r="J8" s="53"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1468,34 +1468,34 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="54"/>
+      <c r="Q8" s="53"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="23">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6">
         <f>B9</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6">
         <f>B9</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="54"/>
+      <c r="J9" s="53"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1508,34 +1508,34 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="54"/>
+      <c r="Q9" s="53"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="29">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6">
         <f>B10</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="26">
         <f>B10</f>
-        <v>10</v>
-      </c>
-      <c r="J10" s="54"/>
+        <v>8</v>
+      </c>
+      <c r="J10" s="53"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="54"/>
+      <c r="Q10" s="53"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1569,7 +1569,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="54"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1578,14 +1578,14 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="54"/>
+      <c r="Q11" s="53"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="32">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>22</v>
@@ -1593,16 +1593,16 @@
       <c r="D12" s="29"/>
       <c r="E12" s="38">
         <f>B12</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F12" s="6">
         <f>B12</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="54"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1613,7 +1613,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="54"/>
+      <c r="Q12" s="53"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1629,12 +1629,12 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
-        <f t="shared" ref="G13:G20" si="2">B13</f>
+        <f t="shared" ref="G13:G17" si="2">B13</f>
         <v>10</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="54"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="54"/>
+      <c r="Q13" s="53"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="54"/>
+      <c r="J14" s="53"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="54"/>
+      <c r="Q14" s="53"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="54"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="54"/>
+      <c r="Q15" s="53"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1745,7 +1745,7 @@
         <f>B16</f>
         <v>10</v>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1758,7 +1758,7 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="54"/>
+      <c r="Q16" s="53"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1785,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="54"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="54"/>
+      <c r="Q17" s="53"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1828,7 +1828,7 @@
         <f>B18</f>
         <v>5</v>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="53"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1843,7 +1843,7 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="54"/>
+      <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1867,7 +1867,7 @@
         <f>B19</f>
         <v>10</v>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1878,7 +1878,7 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="54"/>
+      <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1899,7 +1899,7 @@
         <f>B20</f>
         <v>10</v>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="53"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1908,37 +1908,37 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="54"/>
+      <c r="Q20" s="53"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="60"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="3">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
-        <v>10.833333333333334</v>
+        <v>11.158333333333333</v>
       </c>
       <c r="E21" s="30">
         <f t="shared" si="3"/>
-        <v>10.108333333333333</v>
+        <v>9.85</v>
       </c>
       <c r="F21" s="30">
         <f t="shared" si="3"/>
-        <v>10.633333333333333</v>
+        <v>9.2416666666666671</v>
       </c>
       <c r="G21" s="30">
         <f t="shared" si="3"/>
-        <v>10.083333333333334</v>
+        <v>10.9</v>
       </c>
       <c r="H21" s="30">
         <f t="shared" si="3"/>
-        <v>9.4166666666666661</v>
+        <v>8.8166666666666664</v>
       </c>
       <c r="I21" s="30">
         <f t="shared" si="3"/>
-        <v>9.3333333333333339</v>
-      </c>
-      <c r="J21" s="54"/>
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="J21" s="53"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1957,7 +1957,7 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="54"/>
+      <c r="Q21" s="53"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1965,34 +1965,34 @@
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
-        <v>10.040833333333333</v>
+        <v>11.513333333333334</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="7">
         <f t="shared" ref="D22:I22" si="4">((D21*K21)+(D5*K5))/K22</f>
-        <v>10.5</v>
+        <v>12.295</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="4"/>
-        <v>10.065</v>
+        <v>11.51</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="4"/>
-        <v>10.38</v>
+        <v>11.145</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="4"/>
-        <v>10.050000000000001</v>
+        <v>12.14</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="4"/>
-        <v>9.65</v>
+        <v>10.89</v>
       </c>
       <c r="I22" s="30">
         <f t="shared" si="4"/>
-        <v>9.6</v>
-      </c>
-      <c r="J22" s="54"/>
+        <v>11.1</v>
+      </c>
+      <c r="J22" s="53"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -2011,85 +2011,85 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="54"/>
+      <c r="Q22" s="53"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="54"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="53"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
@@ -2112,7 +2112,7 @@
       <c r="I27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="54"/>
+      <c r="J27" s="53"/>
       <c r="K27" s="9" t="s">
         <v>0</v>
       </c>
@@ -2131,7 +2131,7 @@
       <c r="P27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="54"/>
+      <c r="Q27" s="53"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
@@ -2165,7 +2165,7 @@
         <f>C28</f>
         <v>10</v>
       </c>
-      <c r="J28" s="54"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2184,7 +2184,7 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="54"/>
+      <c r="Q28" s="53"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
@@ -2218,7 +2218,7 @@
         <f>C29</f>
         <v>10</v>
       </c>
-      <c r="J29" s="54"/>
+      <c r="J29" s="53"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="54"/>
+      <c r="Q29" s="53"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
@@ -2271,7 +2271,7 @@
         <f>C30</f>
         <v>10</v>
       </c>
-      <c r="J30" s="54"/>
+      <c r="J30" s="53"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2290,7 +2290,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="54"/>
+      <c r="Q30" s="53"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2320,7 +2320,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="J31" s="54"/>
+      <c r="J31" s="53"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2339,7 +2339,7 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="54"/>
+      <c r="Q31" s="53"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -2349,20 +2349,20 @@
         <v>8</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="56"/>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="54"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="53"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2389,7 +2389,7 @@
         <f>$B33</f>
         <v>10</v>
       </c>
-      <c r="J33" s="54"/>
+      <c r="J33" s="53"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2402,7 +2402,7 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="54"/>
+      <c r="Q33" s="53"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2426,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="54"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="54"/>
+      <c r="Q34" s="53"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="54"/>
+      <c r="J35" s="53"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="54"/>
+      <c r="Q35" s="53"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2488,7 +2488,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="54"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2497,7 +2497,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="54"/>
+      <c r="Q36" s="53"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2521,7 +2521,7 @@
         <f>$B37</f>
         <v>10</v>
       </c>
-      <c r="J37" s="54"/>
+      <c r="J37" s="53"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2532,7 +2532,7 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="54"/>
+      <c r="Q37" s="53"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2556,7 +2556,7 @@
         <f>B38</f>
         <v>10</v>
       </c>
-      <c r="J38" s="54"/>
+      <c r="J38" s="53"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2567,7 +2567,7 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="54"/>
+      <c r="Q38" s="53"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2588,7 +2588,7 @@
         <f>$B39</f>
         <v>10</v>
       </c>
-      <c r="J39" s="54"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2597,7 +2597,7 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="54"/>
+      <c r="Q39" s="53"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2618,7 +2618,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="54"/>
+      <c r="J40" s="53"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2627,7 +2627,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="54"/>
+      <c r="Q40" s="53"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2651,7 +2651,7 @@
         <v>10</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="54"/>
+      <c r="J41" s="53"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2662,7 +2662,7 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="54"/>
+      <c r="Q41" s="53"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -2692,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="54"/>
+      <c r="J42" s="53"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="54"/>
+      <c r="Q42" s="53"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2737,7 +2737,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="54"/>
+      <c r="J43" s="53"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="54"/>
+      <c r="Q43" s="53"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2773,7 +2773,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="54"/>
+      <c r="J44" s="53"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2782,12 +2782,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="54"/>
+      <c r="Q44" s="53"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="6">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>10</v>
@@ -2812,7 +2812,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="J45" s="54"/>
+      <c r="J45" s="53"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2831,7 +2831,7 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="54"/>
+      <c r="Q45" s="53"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -2866,7 +2866,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="J46" s="54"/>
+      <c r="J46" s="53"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2885,128 +2885,128 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="54"/>
+      <c r="Q46" s="53"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="54"/>
-      <c r="L47" s="54"/>
-      <c r="M47" s="54"/>
-      <c r="N47" s="54"/>
-      <c r="O47" s="54"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="54"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="53"/>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="53"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="54"/>
-      <c r="K48" s="54"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="54"/>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="53"/>
+      <c r="P49" s="53"/>
+      <c r="Q49" s="53"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
-      <c r="J50" s="54"/>
-      <c r="K50" s="54"/>
-      <c r="L50" s="54"/>
-      <c r="M50" s="54"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="54"/>
-      <c r="P50" s="54"/>
-      <c r="Q50" s="54"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="53"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="53"/>
+      <c r="O50" s="53"/>
+      <c r="P50" s="53"/>
+      <c r="Q50" s="53"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
+      <c r="A51" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="53"/>
-      <c r="M51" s="53"/>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="53"/>
-      <c r="Q51" s="54"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="59"/>
+      <c r="M51" s="59"/>
+      <c r="N51" s="59"/>
+      <c r="O51" s="59"/>
+      <c r="P51" s="59"/>
+      <c r="Q51" s="53"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="54"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="53"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="54"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
       <c r="D53" s="3" t="s">
         <v>0</v>
       </c>
@@ -3025,92 +3025,97 @@
       <c r="I53" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="54"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="53"/>
+      <c r="O53" s="53"/>
+      <c r="P53" s="53"/>
+      <c r="Q53" s="53"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="54"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="8">(D46+D22)/2</f>
-        <v>10.25</v>
+        <v>11.147500000000001</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="8"/>
-        <v>10.032499999999999</v>
+        <v>10.754999999999999</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="8"/>
-        <v>10.190000000000001</v>
+        <v>10.5725</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="8"/>
-        <v>10.025</v>
+        <v>11.07</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="8"/>
-        <v>9.8249999999999993</v>
+        <v>10.445</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="8"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J54" s="54"/>
-      <c r="K54" s="54"/>
-      <c r="L54" s="54"/>
-      <c r="M54" s="54"/>
-      <c r="N54" s="54"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="54"/>
-      <c r="Q54" s="54"/>
+        <v>10.55</v>
+      </c>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="53"/>
+      <c r="M54" s="53"/>
+      <c r="N54" s="53"/>
+      <c r="O54" s="53"/>
+      <c r="P54" s="53"/>
+      <c r="Q54" s="53"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="54"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="M55" s="54"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="54"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="53"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
-      <c r="M56" s="54"/>
-      <c r="N56" s="54"/>
-      <c r="O56" s="54"/>
-      <c r="P56" s="54"/>
-      <c r="Q56" s="54"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
+      <c r="M56" s="53"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="53"/>
+      <c r="P56" s="53"/>
+      <c r="Q56" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3127,11 +3132,6 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">

--- a/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
@@ -14,25 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
-  <si>
-    <t>UE1.1</t>
-  </si>
-  <si>
-    <t>UE1.2</t>
-  </si>
-  <si>
-    <t>UE1.3</t>
-  </si>
-  <si>
-    <t>UE1.4</t>
-  </si>
-  <si>
-    <t>UE1.5</t>
-  </si>
-  <si>
-    <t>UE1.6</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
   <si>
     <t>à remplir</t>
   </si>
@@ -227,6 +209,42 @@
   </si>
   <si>
     <t>Virtualisation</t>
+  </si>
+  <si>
+    <t>UE4.1</t>
+  </si>
+  <si>
+    <t>UE4.2</t>
+  </si>
+  <si>
+    <t>UE4.3</t>
+  </si>
+  <si>
+    <t>UE4.4</t>
+  </si>
+  <si>
+    <t>UE4.5</t>
+  </si>
+  <si>
+    <t>UE4.6</t>
+  </si>
+  <si>
+    <t>UE1</t>
+  </si>
+  <si>
+    <t>UE2</t>
+  </si>
+  <si>
+    <t>UE3</t>
+  </si>
+  <si>
+    <t>UE4</t>
+  </si>
+  <si>
+    <t>UE5</t>
+  </si>
+  <si>
+    <t>UE6</t>
   </si>
 </sst>
 </file>
@@ -854,9 +872,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,18 +894,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1192,93 +1210,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="53"/>
+      <c r="A1" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="54"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="53"/>
+        <v>57</v>
+      </c>
+      <c r="J3" s="54"/>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q3" s="53"/>
+        <v>57</v>
+      </c>
+      <c r="Q3" s="54"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="32">
         <v>14</v>
       </c>
@@ -1306,21 +1324,21 @@
         <f>C4</f>
         <v>14</v>
       </c>
-      <c r="J4" s="53"/>
+      <c r="J4" s="54"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="54"/>
       <c r="S4" s="31" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
@@ -1346,7 +1364,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="J5" s="53"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1365,40 +1383,40 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="53"/>
+      <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="53"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B7" s="32">
         <v>16.899999999999999</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7" s="25">
         <f t="shared" ref="D7:D17" si="1">B7</f>
@@ -1418,7 +1436,7 @@
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1433,17 +1451,17 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B8" s="32">
         <v>12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D8" s="23">
         <f t="shared" si="1"/>
@@ -1457,7 +1475,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1468,17 +1486,17 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="53"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="32">
         <v>8</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D9" s="23">
         <f t="shared" si="1"/>
@@ -1495,7 +1513,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1508,17 +1526,17 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="53"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" s="32">
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D10" s="29">
         <f t="shared" si="1"/>
@@ -1535,7 +1553,7 @@
         <f>B10</f>
         <v>8</v>
       </c>
-      <c r="J10" s="53"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1548,17 +1566,17 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="53"/>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B11" s="32">
         <v>12</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="6"/>
@@ -1569,7 +1587,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1578,17 +1596,17 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="53"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="32">
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="38">
@@ -1602,7 +1620,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1613,17 +1631,17 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="53"/>
+      <c r="Q12" s="54"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B13" s="32">
         <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="6"/>
@@ -1634,7 +1652,7 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="53"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1643,17 +1661,17 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="53"/>
+      <c r="Q13" s="54"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B14" s="32">
         <v>11.5</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="6">
@@ -1667,7 +1685,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1678,17 +1696,17 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="53"/>
+      <c r="Q14" s="54"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B15" s="32">
         <v>5.5</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D15" s="29"/>
       <c r="E15" s="6">
@@ -1705,7 +1723,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="53"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1718,17 +1736,17 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="53"/>
+      <c r="Q15" s="54"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" s="32">
         <v>10</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16" s="29"/>
       <c r="E16" s="6"/>
@@ -1745,7 +1763,7 @@
         <f>B16</f>
         <v>10</v>
       </c>
-      <c r="J16" s="53"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1758,17 +1776,17 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="53"/>
+      <c r="Q16" s="54"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B17" s="32">
         <v>10</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D17" s="23">
         <f t="shared" si="1"/>
@@ -1785,7 +1803,7 @@
         <v>10</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1798,37 +1816,37 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="53"/>
+      <c r="Q17" s="54"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B18" s="32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="6">
         <f>B18</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="24">
         <f>B18</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
         <f>B18</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="26">
         <f>B18</f>
-        <v>5</v>
-      </c>
-      <c r="J18" s="53"/>
+        <v>6</v>
+      </c>
+      <c r="J18" s="54"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1843,17 +1861,17 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="53"/>
+      <c r="Q18" s="54"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B19" s="32">
         <v>10</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D19" s="29"/>
       <c r="E19" s="6"/>
@@ -1867,7 +1885,7 @@
         <f>B19</f>
         <v>10</v>
       </c>
-      <c r="J19" s="53"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1878,17 +1896,17 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="53"/>
+      <c r="Q19" s="54"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B20" s="32">
         <v>10</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
@@ -1899,7 +1917,7 @@
         <f>B20</f>
         <v>10</v>
       </c>
-      <c r="J20" s="53"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1908,23 +1926,23 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="53"/>
+      <c r="Q20" s="54"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="56"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="3">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
         <v>11.158333333333333</v>
       </c>
       <c r="E21" s="30">
         <f t="shared" si="3"/>
-        <v>9.85</v>
+        <v>9.9333333333333336</v>
       </c>
       <c r="F21" s="30">
         <f t="shared" si="3"/>
-        <v>9.2416666666666671</v>
+        <v>9.3249999999999993</v>
       </c>
       <c r="G21" s="30">
         <f t="shared" si="3"/>
@@ -1932,13 +1950,13 @@
       </c>
       <c r="H21" s="30">
         <f t="shared" si="3"/>
-        <v>8.8166666666666664</v>
+        <v>8.9333333333333336</v>
       </c>
       <c r="I21" s="30">
         <f t="shared" si="3"/>
-        <v>9.1666666666666661</v>
-      </c>
-      <c r="J21" s="53"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J21" s="54"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1957,15 +1975,15 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="53"/>
+      <c r="Q21" s="54"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
-        <v>11.513333333333334</v>
+        <v>11.555</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="7">
@@ -1974,11 +1992,11 @@
       </c>
       <c r="E22" s="7">
         <f t="shared" si="4"/>
-        <v>11.51</v>
+        <v>11.56</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="4"/>
-        <v>11.145</v>
+        <v>11.195</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="4"/>
@@ -1986,13 +2004,13 @@
       </c>
       <c r="H22" s="7">
         <f t="shared" si="4"/>
-        <v>10.89</v>
+        <v>10.96</v>
       </c>
       <c r="I22" s="30">
         <f t="shared" si="4"/>
-        <v>11.1</v>
-      </c>
-      <c r="J22" s="53"/>
+        <v>11.18</v>
+      </c>
+      <c r="J22" s="54"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -2011,132 +2029,132 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="53"/>
+      <c r="Q22" s="54"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="53"/>
+      <c r="A25" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
       <c r="D27" s="9" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="53"/>
+        <v>70</v>
+      </c>
+      <c r="J27" s="54"/>
       <c r="K27" s="9" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="P27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="53"/>
+        <v>70</v>
+      </c>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" s="43">
         <v>10</v>
@@ -2165,7 +2183,7 @@
         <f>C28</f>
         <v>10</v>
       </c>
-      <c r="J28" s="53"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2184,12 +2202,12 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="53"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C29" s="43">
         <v>10</v>
@@ -2218,7 +2236,7 @@
         <f>C29</f>
         <v>10</v>
       </c>
-      <c r="J29" s="53"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2237,12 +2255,12 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="53"/>
+      <c r="Q29" s="54"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C30" s="43">
         <v>10</v>
@@ -2271,7 +2289,7 @@
         <f>C30</f>
         <v>10</v>
       </c>
-      <c r="J30" s="53"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2290,7 +2308,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="53"/>
+      <c r="Q30" s="54"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2320,7 +2338,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="J31" s="53"/>
+      <c r="J31" s="54"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2339,40 +2357,40 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="53"/>
+      <c r="Q31" s="54"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="54"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B33" s="32">
         <v>10</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D33" s="25">
         <f>$B33</f>
@@ -2389,7 +2407,7 @@
         <f>$B33</f>
         <v>10</v>
       </c>
-      <c r="J33" s="53"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2402,17 +2420,17 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="53"/>
+      <c r="Q33" s="54"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B34" s="32">
         <v>10</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D34" s="23">
         <f>$B34</f>
@@ -2426,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="53"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2437,17 +2455,17 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="53"/>
+      <c r="Q34" s="54"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="32">
         <v>10</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D35" s="29"/>
       <c r="E35" s="6"/>
@@ -2458,7 +2476,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="53"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2467,17 +2485,17 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="53"/>
+      <c r="Q35" s="54"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="32">
+        <v>10</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B36" s="32">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="D36" s="29"/>
       <c r="E36" s="6">
@@ -2488,7 +2506,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="53"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2497,17 +2515,17 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="53"/>
+      <c r="Q36" s="54"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B37" s="32">
         <v>10</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D37" s="29"/>
       <c r="E37" s="6">
@@ -2521,7 +2539,7 @@
         <f>$B37</f>
         <v>10</v>
       </c>
-      <c r="J37" s="53"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2532,17 +2550,17 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="53"/>
+      <c r="Q37" s="54"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B38" s="32">
         <v>10</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D38" s="29"/>
       <c r="E38" s="6"/>
@@ -2556,7 +2574,7 @@
         <f>B38</f>
         <v>10</v>
       </c>
-      <c r="J38" s="53"/>
+      <c r="J38" s="54"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2567,17 +2585,17 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="53"/>
+      <c r="Q38" s="54"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B39" s="32">
         <v>10</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D39" s="29"/>
       <c r="E39" s="6"/>
@@ -2588,7 +2606,7 @@
         <f>$B39</f>
         <v>10</v>
       </c>
-      <c r="J39" s="53"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2597,17 +2615,17 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="53"/>
+      <c r="Q39" s="54"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B40" s="32">
         <v>10</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D40" s="29"/>
       <c r="E40" s="6"/>
@@ -2618,7 +2636,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="53"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2627,17 +2645,17 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="53"/>
+      <c r="Q40" s="54"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B41" s="32">
         <v>10</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D41" s="29"/>
       <c r="E41" s="6">
@@ -2651,7 +2669,7 @@
         <v>10</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="53"/>
+      <c r="J41" s="54"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2662,17 +2680,17 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="53"/>
+      <c r="Q41" s="54"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B42" s="32">
         <v>10</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D42" s="23">
         <f>$B42</f>
@@ -2692,7 +2710,7 @@
         <v>10</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="53"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2707,17 +2725,17 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="53"/>
+      <c r="Q42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B43" s="32">
         <v>10</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D43" s="29">
         <f>B43</f>
@@ -2737,7 +2755,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="53"/>
+      <c r="J43" s="54"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2752,17 +2770,17 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="53"/>
+      <c r="Q43" s="54"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B44" s="32">
         <v>10</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D44" s="33"/>
       <c r="E44" s="34">
@@ -2773,7 +2791,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2782,12 +2800,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="53"/>
+      <c r="Q44" s="54"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="6">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>10</v>
@@ -2812,7 +2830,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="J45" s="53"/>
+      <c r="J45" s="54"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2831,11 +2849,11 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="53"/>
+      <c r="Q45" s="54"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B46" s="6">
         <f>SUM(D46:I46)/6</f>
@@ -2866,7 +2884,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="J46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2885,170 +2903,170 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="53"/>
+      <c r="Q46" s="54"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="53"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="53"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="53"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" s="59"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="53"/>
+      <c r="A51" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="53"/>
+      <c r="P51" s="53"/>
+      <c r="Q51" s="54"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="55"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="53"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="54"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="3" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
-      <c r="N53" s="53"/>
-      <c r="O53" s="53"/>
-      <c r="P53" s="53"/>
-      <c r="Q53" s="53"/>
+        <v>76</v>
+      </c>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="54"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="54"/>
+      <c r="Q53" s="54"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="8">(D46+D22)/2</f>
         <v>11.147500000000001</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="8"/>
-        <v>10.754999999999999</v>
+        <v>10.780000000000001</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="8"/>
-        <v>10.5725</v>
+        <v>10.5975</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="8"/>
@@ -3056,66 +3074,61 @@
       </c>
       <c r="H54" s="1">
         <f t="shared" si="8"/>
-        <v>10.445</v>
+        <v>10.48</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="8"/>
-        <v>10.55</v>
-      </c>
-      <c r="J54" s="53"/>
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-      <c r="N54" s="53"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="53"/>
+        <v>10.59</v>
+      </c>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="54"/>
+      <c r="Q54" s="54"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="54"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="53"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3132,6 +3145,11 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">

--- a/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
@@ -872,28 +872,28 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,48 +1210,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="54"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="53"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1273,7 +1273,7 @@
       <c r="I3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="54"/>
+      <c r="J3" s="53"/>
       <c r="K3" s="3" t="s">
         <v>52</v>
       </c>
@@ -1292,11 +1292,11 @@
       <c r="P3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" s="54"/>
+      <c r="Q3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="32">
         <v>14</v>
       </c>
@@ -1324,21 +1324,21 @@
         <f>C4</f>
         <v>14</v>
       </c>
-      <c r="J4" s="54"/>
+      <c r="J4" s="53"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="53"/>
       <c r="S4" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
@@ -1364,7 +1364,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="J5" s="54"/>
+      <c r="J5" s="53"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1383,7 +1383,7 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="54"/>
+      <c r="Q5" s="53"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1393,20 +1393,20 @@
         <v>2</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="54"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="53"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="54"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="54"/>
+      <c r="Q7" s="53"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1475,7 +1475,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="54"/>
+      <c r="J8" s="53"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1486,34 +1486,34 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="54"/>
+      <c r="Q8" s="53"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="32">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="23">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="E9" s="6">
         <f>B9</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6">
         <f>B9</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="54"/>
+      <c r="J9" s="53"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="54"/>
+      <c r="Q9" s="53"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1553,7 +1553,7 @@
         <f>B10</f>
         <v>8</v>
       </c>
-      <c r="J10" s="54"/>
+      <c r="J10" s="53"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="54"/>
+      <c r="Q10" s="53"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1587,7 +1587,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="54"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1596,7 +1596,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="54"/>
+      <c r="Q11" s="53"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1620,7 +1620,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="54"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1631,7 +1631,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="54"/>
+      <c r="Q12" s="53"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="54"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="54"/>
+      <c r="Q13" s="53"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="54"/>
+      <c r="J14" s="53"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="54"/>
+      <c r="Q14" s="53"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="54"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="54"/>
+      <c r="Q15" s="53"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1763,7 +1763,7 @@
         <f>B16</f>
         <v>10</v>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1776,34 +1776,34 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="54"/>
+      <c r="Q16" s="53"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B17" s="32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="23">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="24"/>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H17" s="6">
         <f>B17</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="54"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="54"/>
+      <c r="Q17" s="53"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1846,7 +1846,7 @@
         <f>B18</f>
         <v>6</v>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="53"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="54"/>
+      <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1885,7 +1885,7 @@
         <f>B19</f>
         <v>10</v>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1896,7 +1896,7 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="54"/>
+      <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1917,7 +1917,7 @@
         <f>B20</f>
         <v>10</v>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="53"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1926,19 +1926,19 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="54"/>
+      <c r="Q20" s="53"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="60"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="3">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
-        <v>11.158333333333333</v>
+        <v>11.525</v>
       </c>
       <c r="E21" s="30">
         <f t="shared" si="3"/>
-        <v>9.9333333333333336</v>
+        <v>10.058333333333334</v>
       </c>
       <c r="F21" s="30">
         <f t="shared" si="3"/>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="G21" s="30">
         <f t="shared" si="3"/>
-        <v>10.9</v>
+        <v>10.941666666666666</v>
       </c>
       <c r="H21" s="30">
         <f t="shared" si="3"/>
-        <v>8.9333333333333336</v>
+        <v>9.2666666666666675</v>
       </c>
       <c r="I21" s="30">
         <f t="shared" si="3"/>
         <v>9.3000000000000007</v>
       </c>
-      <c r="J21" s="54"/>
+      <c r="J21" s="53"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1975,7 +1975,7 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="54"/>
+      <c r="Q21" s="53"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1983,16 +1983,16 @@
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
-        <v>11.555</v>
+        <v>11.641666666666666</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="7">
         <f t="shared" ref="D22:I22" si="4">((D21*K21)+(D5*K5))/K22</f>
-        <v>12.295</v>
+        <v>12.515000000000001</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="4"/>
-        <v>11.56</v>
+        <v>11.635</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="4"/>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="G22" s="7">
         <f t="shared" si="4"/>
-        <v>12.14</v>
+        <v>12.164999999999999</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="4"/>
-        <v>10.96</v>
+        <v>11.16</v>
       </c>
       <c r="I22" s="30">
         <f t="shared" si="4"/>
         <v>11.18</v>
       </c>
-      <c r="J22" s="54"/>
+      <c r="J22" s="53"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -2029,85 +2029,85 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="54"/>
+      <c r="Q22" s="53"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="54"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="53"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
@@ -2130,7 +2130,7 @@
       <c r="I27" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="54"/>
+      <c r="J27" s="53"/>
       <c r="K27" s="9" t="s">
         <v>65</v>
       </c>
@@ -2149,7 +2149,7 @@
       <c r="P27" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q27" s="54"/>
+      <c r="Q27" s="53"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
@@ -2183,7 +2183,7 @@
         <f>C28</f>
         <v>10</v>
       </c>
-      <c r="J28" s="54"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2202,7 +2202,7 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="54"/>
+      <c r="Q28" s="53"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
@@ -2236,7 +2236,7 @@
         <f>C29</f>
         <v>10</v>
       </c>
-      <c r="J29" s="54"/>
+      <c r="J29" s="53"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2255,7 +2255,7 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="54"/>
+      <c r="Q29" s="53"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
@@ -2289,7 +2289,7 @@
         <f>C30</f>
         <v>10</v>
       </c>
-      <c r="J30" s="54"/>
+      <c r="J30" s="53"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2308,7 +2308,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="54"/>
+      <c r="Q30" s="53"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2338,7 +2338,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="J31" s="54"/>
+      <c r="J31" s="53"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2357,7 +2357,7 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="54"/>
+      <c r="Q31" s="53"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -2367,20 +2367,20 @@
         <v>2</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="56"/>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="54"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="53"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2407,7 +2407,7 @@
         <f>$B33</f>
         <v>10</v>
       </c>
-      <c r="J33" s="54"/>
+      <c r="J33" s="53"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="54"/>
+      <c r="Q33" s="53"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="54"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="54"/>
+      <c r="Q34" s="53"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="54"/>
+      <c r="J35" s="53"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="54"/>
+      <c r="Q35" s="53"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2506,7 +2506,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="54"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2515,7 +2515,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="54"/>
+      <c r="Q36" s="53"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2539,7 +2539,7 @@
         <f>$B37</f>
         <v>10</v>
       </c>
-      <c r="J37" s="54"/>
+      <c r="J37" s="53"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2550,7 +2550,7 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="54"/>
+      <c r="Q37" s="53"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2574,7 +2574,7 @@
         <f>B38</f>
         <v>10</v>
       </c>
-      <c r="J38" s="54"/>
+      <c r="J38" s="53"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2585,7 +2585,7 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="54"/>
+      <c r="Q38" s="53"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2606,7 +2606,7 @@
         <f>$B39</f>
         <v>10</v>
       </c>
-      <c r="J39" s="54"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2615,7 +2615,7 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="54"/>
+      <c r="Q39" s="53"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2636,7 +2636,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="54"/>
+      <c r="J40" s="53"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2645,7 +2645,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="54"/>
+      <c r="Q40" s="53"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2669,7 +2669,7 @@
         <v>10</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="54"/>
+      <c r="J41" s="53"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2680,7 +2680,7 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="54"/>
+      <c r="Q41" s="53"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -2710,7 +2710,7 @@
         <v>10</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="54"/>
+      <c r="J42" s="53"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="54"/>
+      <c r="Q42" s="53"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2755,7 +2755,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="54"/>
+      <c r="J43" s="53"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="54"/>
+      <c r="Q43" s="53"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2791,7 +2791,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="54"/>
+      <c r="J44" s="53"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2800,12 +2800,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="54"/>
+      <c r="Q44" s="53"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="6">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>10</v>
@@ -2830,7 +2830,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="J45" s="54"/>
+      <c r="J45" s="53"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2849,7 +2849,7 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="54"/>
+      <c r="Q45" s="53"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -2884,7 +2884,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="J46" s="54"/>
+      <c r="J46" s="53"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2903,128 +2903,128 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="54"/>
+      <c r="Q46" s="53"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="54"/>
-      <c r="L47" s="54"/>
-      <c r="M47" s="54"/>
-      <c r="N47" s="54"/>
-      <c r="O47" s="54"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="54"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="53"/>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="53"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="54"/>
-      <c r="K48" s="54"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="54"/>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="53"/>
+      <c r="P49" s="53"/>
+      <c r="Q49" s="53"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
-      <c r="J50" s="54"/>
-      <c r="K50" s="54"/>
-      <c r="L50" s="54"/>
-      <c r="M50" s="54"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="54"/>
-      <c r="P50" s="54"/>
-      <c r="Q50" s="54"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="53"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="53"/>
+      <c r="O50" s="53"/>
+      <c r="P50" s="53"/>
+      <c r="Q50" s="53"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
+      <c r="A51" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="53"/>
-      <c r="M51" s="53"/>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="53"/>
-      <c r="Q51" s="54"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="59"/>
+      <c r="M51" s="59"/>
+      <c r="N51" s="59"/>
+      <c r="O51" s="59"/>
+      <c r="P51" s="59"/>
+      <c r="Q51" s="53"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="54"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="53"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="54"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
       <c r="D53" s="3" t="s">
         <v>71</v>
       </c>
@@ -3043,26 +3043,26 @@
       <c r="I53" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="54"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="53"/>
+      <c r="O53" s="53"/>
+      <c r="P53" s="53"/>
+      <c r="Q53" s="53"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="54"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="8">(D46+D22)/2</f>
-        <v>11.147500000000001</v>
+        <v>11.2575</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="8"/>
-        <v>10.780000000000001</v>
+        <v>10.817499999999999</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="8"/>
@@ -3070,65 +3070,70 @@
       </c>
       <c r="G54" s="1">
         <f t="shared" si="8"/>
-        <v>11.07</v>
+        <v>11.0825</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="8"/>
-        <v>10.48</v>
+        <v>10.58</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="8"/>
         <v>10.59</v>
       </c>
-      <c r="J54" s="54"/>
-      <c r="K54" s="54"/>
-      <c r="L54" s="54"/>
-      <c r="M54" s="54"/>
-      <c r="N54" s="54"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="54"/>
-      <c r="Q54" s="54"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="53"/>
+      <c r="M54" s="53"/>
+      <c r="N54" s="53"/>
+      <c r="O54" s="53"/>
+      <c r="P54" s="53"/>
+      <c r="Q54" s="53"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="54"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="M55" s="54"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="54"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="53"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
-      <c r="M56" s="54"/>
-      <c r="N56" s="54"/>
-      <c r="O56" s="54"/>
-      <c r="P56" s="54"/>
-      <c r="Q56" s="54"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
+      <c r="M56" s="53"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="53"/>
+      <c r="P56" s="53"/>
+      <c r="Q56" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3145,11 +3150,6 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">

--- a/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
@@ -1298,31 +1298,31 @@
       <c r="A4" s="53"/>
       <c r="B4" s="53"/>
       <c r="C4" s="32">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" s="39">
         <f>C4</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="40">
         <f>C4</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" s="40">
         <f>C4</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4" s="40">
         <f>C4</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" s="40">
         <f>C4</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" s="41">
         <f>C4</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" s="53"/>
       <c r="K4" s="12"/>
@@ -1342,27 +1342,27 @@
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" ref="E5:I5" si="0">(E4*L5)/L5</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" s="21">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5" s="21">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5" s="21">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" s="22">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J5" s="53"/>
       <c r="K5" s="17">
@@ -1458,18 +1458,18 @@
         <v>24</v>
       </c>
       <c r="B8" s="32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="23">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" s="6">
         <f>B8</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -1533,25 +1533,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="32">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="29">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6">
         <f>B10</f>
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="I10" s="26">
         <f>B10</f>
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="J10" s="53"/>
       <c r="K10" s="15">
@@ -1573,7 +1573,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>15</v>
@@ -1582,7 +1582,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6">
         <f>B11</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -1668,7 +1668,8 @@
         <v>28</v>
       </c>
       <c r="B14" s="32">
-        <v>11.5</v>
+        <f>(11.5+6)/2</f>
+        <v>8.75</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>18</v>
@@ -1676,12 +1677,12 @@
       <c r="D14" s="29"/>
       <c r="E14" s="6">
         <f>B14</f>
-        <v>11.5</v>
+        <v>8.75</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6">
         <f t="shared" si="2"/>
-        <v>11.5</v>
+        <v>8.75</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
@@ -1703,7 +1704,8 @@
         <v>29</v>
       </c>
       <c r="B15" s="32">
-        <v>5.5</v>
+        <f>(7.5+5.5)/2</f>
+        <v>6.5</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>19</v>
@@ -1711,15 +1713,15 @@
       <c r="D15" s="29"/>
       <c r="E15" s="6">
         <f>B15</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F15" s="6">
         <f>B15</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
@@ -1823,7 +1825,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="32">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>22</v>
@@ -1831,20 +1833,20 @@
       <c r="D18" s="23"/>
       <c r="E18" s="6">
         <f>B18</f>
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="F18" s="24">
         <f>B18</f>
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
         <f>B18</f>
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="I18" s="26">
         <f>B18</f>
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="J18" s="53"/>
       <c r="K18" s="15"/>
@@ -1868,7 +1870,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>32</v>
@@ -1879,11 +1881,11 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6">
         <f>B19</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I19" s="26">
         <f>B19</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" s="53"/>
       <c r="K19" s="15"/>
@@ -1934,27 +1936,27 @@
       <c r="C21" s="56"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="3">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
-        <v>11.525</v>
+        <v>12.233333333333333</v>
       </c>
       <c r="E21" s="30">
         <f t="shared" si="3"/>
-        <v>10.058333333333334</v>
+        <v>9.2041666666666675</v>
       </c>
       <c r="F21" s="30">
         <f t="shared" si="3"/>
-        <v>9.3249999999999993</v>
+        <v>8.65</v>
       </c>
       <c r="G21" s="30">
         <f t="shared" si="3"/>
-        <v>10.941666666666666</v>
+        <v>10.795833333333333</v>
       </c>
       <c r="H21" s="30">
         <f t="shared" si="3"/>
-        <v>9.2666666666666675</v>
+        <v>11.108333333333333</v>
       </c>
       <c r="I21" s="30">
         <f t="shared" si="3"/>
-        <v>9.3000000000000007</v>
+        <v>11.291666666666666</v>
       </c>
       <c r="J21" s="53"/>
       <c r="K21" s="17">
@@ -1983,32 +1985,32 @@
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
-        <v>11.641666666666666</v>
+        <v>11.128333333333336</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="7">
         <f t="shared" ref="D22:I22" si="4">((D21*K21)+(D5*K5))/K22</f>
-        <v>12.515000000000001</v>
+        <v>12.14</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="4"/>
-        <v>11.635</v>
+        <v>10.3225</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="4"/>
-        <v>11.195</v>
+        <v>9.99</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="4"/>
-        <v>12.164999999999999</v>
+        <v>11.2775</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="4"/>
-        <v>11.16</v>
+        <v>11.465</v>
       </c>
       <c r="I22" s="30">
         <f t="shared" si="4"/>
-        <v>11.18</v>
+        <v>11.574999999999999</v>
       </c>
       <c r="J22" s="53"/>
       <c r="K22" s="3">
@@ -3058,27 +3060,27 @@
       <c r="C54" s="53"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="8">(D46+D22)/2</f>
-        <v>11.2575</v>
+        <v>11.07</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="8"/>
-        <v>10.817499999999999</v>
+        <v>10.161249999999999</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="8"/>
-        <v>10.5975</v>
+        <v>9.995000000000001</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="8"/>
-        <v>11.0825</v>
+        <v>10.63875</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="8"/>
-        <v>10.58</v>
+        <v>10.7325</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="8"/>
-        <v>10.59</v>
+        <v>10.7875</v>
       </c>
       <c r="J54" s="53"/>
       <c r="K54" s="53"/>

--- a/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_Dorian.xlsx
@@ -872,9 +872,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -882,18 +894,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,48 +1210,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="53"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="54"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1273,7 +1273,7 @@
       <c r="I3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="53"/>
+      <c r="J3" s="54"/>
       <c r="K3" s="3" t="s">
         <v>52</v>
       </c>
@@ -1292,11 +1292,11 @@
       <c r="P3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" s="53"/>
+      <c r="Q3" s="54"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="32">
         <v>12</v>
       </c>
@@ -1324,21 +1324,21 @@
         <f>C4</f>
         <v>12</v>
       </c>
-      <c r="J4" s="53"/>
+      <c r="J4" s="54"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="54"/>
       <c r="S4" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
@@ -1364,7 +1364,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="J5" s="53"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1383,7 +1383,7 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="53"/>
+      <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1393,50 +1393,51 @@
         <v>2</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="53"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="32">
-        <v>16.899999999999999</v>
+        <f>(16.9+17.2)/2</f>
+        <v>17.049999999999997</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="25">
         <f t="shared" ref="D7:D17" si="1">B7</f>
-        <v>16.899999999999999</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="E7" s="27">
         <f>B7</f>
-        <v>16.899999999999999</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="F7" s="27">
         <f>B7</f>
-        <v>16.899999999999999</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="G7" s="27">
         <f>B7</f>
-        <v>16.899999999999999</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1451,7 +1452,7 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1475,7 +1476,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1486,7 +1487,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="53"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1513,7 +1514,7 @@
         <v>9.5</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="53"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1553,7 +1554,7 @@
         <f>B10</f>
         <v>13.5</v>
       </c>
-      <c r="J10" s="53"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1566,7 +1567,7 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="53"/>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1587,7 +1588,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1596,7 +1597,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="53"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1620,7 +1621,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1631,14 +1632,14 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="53"/>
+      <c r="Q12" s="54"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="32">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>17</v>
@@ -1648,11 +1649,11 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6">
         <f t="shared" ref="G13:G17" si="2">B13</f>
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="53"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1661,7 +1662,7 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="53"/>
+      <c r="Q13" s="54"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1686,7 +1687,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1697,7 +1698,7 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="53"/>
+      <c r="Q14" s="54"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1725,7 +1726,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="53"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1738,7 +1739,7 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="53"/>
+      <c r="Q15" s="54"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1765,7 +1766,7 @@
         <f>B16</f>
         <v>10</v>
       </c>
-      <c r="J16" s="53"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1778,7 +1779,7 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="53"/>
+      <c r="Q16" s="54"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1805,7 +1806,7 @@
         <v>10.5</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="53"/>
+      <c r="Q17" s="54"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1848,7 +1849,7 @@
         <f>B18</f>
         <v>13.5</v>
       </c>
-      <c r="J18" s="53"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1863,7 +1864,7 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="53"/>
+      <c r="Q18" s="54"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1887,7 +1888,7 @@
         <f>B19</f>
         <v>12</v>
       </c>
-      <c r="J19" s="53"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1898,7 +1899,7 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="53"/>
+      <c r="Q19" s="54"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1919,7 +1920,7 @@
         <f>B20</f>
         <v>10</v>
       </c>
-      <c r="J20" s="53"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1928,27 +1929,27 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="53"/>
+      <c r="Q20" s="54"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="56"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="3">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
-        <v>12.233333333333333</v>
+        <v>12.270833333333334</v>
       </c>
       <c r="E21" s="30">
         <f t="shared" si="3"/>
-        <v>9.2041666666666675</v>
+        <v>9.2166666666666668</v>
       </c>
       <c r="F21" s="30">
         <f t="shared" si="3"/>
-        <v>8.65</v>
+        <v>8.6624999999999996</v>
       </c>
       <c r="G21" s="30">
         <f t="shared" si="3"/>
-        <v>10.795833333333333</v>
+        <v>13.112500000000001</v>
       </c>
       <c r="H21" s="30">
         <f t="shared" si="3"/>
@@ -1958,7 +1959,7 @@
         <f t="shared" si="3"/>
         <v>11.291666666666666</v>
       </c>
-      <c r="J21" s="53"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1977,7 +1978,7 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="53"/>
+      <c r="Q21" s="54"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1985,24 +1986,24 @@
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
-        <v>11.128333333333336</v>
+        <v>11.366250000000001</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="7">
         <f t="shared" ref="D22:I22" si="4">((D21*K21)+(D5*K5))/K22</f>
-        <v>12.14</v>
+        <v>12.1625</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="4"/>
-        <v>10.3225</v>
+        <v>10.33</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="4"/>
-        <v>9.99</v>
+        <v>9.9975000000000005</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="4"/>
-        <v>11.2775</v>
+        <v>12.6675</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="4"/>
@@ -2012,7 +2013,7 @@
         <f t="shared" si="4"/>
         <v>11.574999999999999</v>
       </c>
-      <c r="J22" s="53"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -2031,85 +2032,85 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="53"/>
+      <c r="Q22" s="54"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
@@ -2132,7 +2133,7 @@
       <c r="I27" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="53"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="9" t="s">
         <v>65</v>
       </c>
@@ -2151,7 +2152,7 @@
       <c r="P27" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q27" s="53"/>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
@@ -2185,7 +2186,7 @@
         <f>C28</f>
         <v>10</v>
       </c>
-      <c r="J28" s="53"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2204,7 +2205,7 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="53"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
@@ -2238,7 +2239,7 @@
         <f>C29</f>
         <v>10</v>
       </c>
-      <c r="J29" s="53"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2257,7 +2258,7 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="53"/>
+      <c r="Q29" s="54"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
@@ -2291,7 +2292,7 @@
         <f>C30</f>
         <v>10</v>
       </c>
-      <c r="J30" s="53"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2310,7 +2311,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="53"/>
+      <c r="Q30" s="54"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2340,7 +2341,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="J31" s="53"/>
+      <c r="J31" s="54"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2359,7 +2360,7 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="53"/>
+      <c r="Q31" s="54"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -2369,20 +2370,20 @@
         <v>2</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="54"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2409,7 +2410,7 @@
         <f>$B33</f>
         <v>10</v>
       </c>
-      <c r="J33" s="53"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2422,7 +2423,7 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="53"/>
+      <c r="Q33" s="54"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2446,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="53"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2457,7 +2458,7 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="53"/>
+      <c r="Q34" s="54"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2478,7 +2479,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="53"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="53"/>
+      <c r="Q35" s="54"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2508,7 +2509,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="53"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2517,7 +2518,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="53"/>
+      <c r="Q36" s="54"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2541,7 +2542,7 @@
         <f>$B37</f>
         <v>10</v>
       </c>
-      <c r="J37" s="53"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2552,7 +2553,7 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="53"/>
+      <c r="Q37" s="54"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2576,7 +2577,7 @@
         <f>B38</f>
         <v>10</v>
       </c>
-      <c r="J38" s="53"/>
+      <c r="J38" s="54"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2587,7 +2588,7 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="53"/>
+      <c r="Q38" s="54"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2608,7 +2609,7 @@
         <f>$B39</f>
         <v>10</v>
       </c>
-      <c r="J39" s="53"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2617,7 +2618,7 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="53"/>
+      <c r="Q39" s="54"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2638,7 +2639,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="53"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2647,7 +2648,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="53"/>
+      <c r="Q40" s="54"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2671,7 +2672,7 @@
         <v>10</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="53"/>
+      <c r="J41" s="54"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2682,7 +2683,7 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="53"/>
+      <c r="Q41" s="54"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -2712,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="53"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2727,7 +2728,7 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="53"/>
+      <c r="Q42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2757,7 +2758,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="53"/>
+      <c r="J43" s="54"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2772,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="53"/>
+      <c r="Q43" s="54"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2793,7 +2794,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2802,12 +2803,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="53"/>
+      <c r="Q44" s="54"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="6">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>10</v>
@@ -2832,7 +2833,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="J45" s="53"/>
+      <c r="J45" s="54"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2851,7 +2852,7 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="53"/>
+      <c r="Q45" s="54"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -2886,7 +2887,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="J46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2905,128 +2906,128 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="53"/>
+      <c r="Q46" s="54"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="53"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="53"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="53"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="59" t="s">
+      <c r="A51" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="59"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="53"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="53"/>
+      <c r="P51" s="53"/>
+      <c r="Q51" s="54"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="55"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="53"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="54"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="3" t="s">
         <v>71</v>
       </c>
@@ -3045,34 +3046,34 @@
       <c r="I53" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
-      <c r="N53" s="53"/>
-      <c r="O53" s="53"/>
-      <c r="P53" s="53"/>
-      <c r="Q53" s="53"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="54"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="54"/>
+      <c r="Q53" s="54"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="8">(D46+D22)/2</f>
-        <v>11.07</v>
+        <v>11.081250000000001</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="8"/>
-        <v>10.161249999999999</v>
+        <v>10.164999999999999</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="8"/>
-        <v>9.995000000000001</v>
+        <v>9.9987500000000011</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="8"/>
-        <v>10.63875</v>
+        <v>11.33375</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="8"/>
@@ -3082,60 +3083,55 @@
         <f t="shared" si="8"/>
         <v>10.7875</v>
       </c>
-      <c r="J54" s="53"/>
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-      <c r="N54" s="53"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="53"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="54"/>
+      <c r="Q54" s="54"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="54"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="53"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3152,6 +3148,11 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">
